--- a/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
+++ b/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:05:42+00:00</t>
+    <t>2026-10-14T07:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
+++ b/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:28:35+00:00</t>
+    <t>2026-10-14T07:51:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
+++ b/branches/test/promis29-testscripts-ig/StructureDefinition-mii-pr-pro-observation-phq-9.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:24+00:00</t>
+    <t>2026-10-14T08:29:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
